--- a/output/roomself_excel/14853.xlsx
+++ b/output/roomself_excel/14853.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120384</v>
+        <v>191315</v>
       </c>
       <c r="D2" t="n">
-        <v>3224</v>
+        <v>3696</v>
       </c>
       <c r="E2" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>341696</v>
+        <v>179365</v>
       </c>
       <c r="D3" t="n">
-        <v>4680</v>
+        <v>3432</v>
       </c>
       <c r="E3" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>562879</v>
+        <v>116675</v>
       </c>
       <c r="D4" t="n">
-        <v>11032</v>
+        <v>2736</v>
       </c>
       <c r="E4" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72492</v>
+        <v>100520</v>
       </c>
       <c r="D5" t="n">
-        <v>2412</v>
+        <v>2556</v>
       </c>
       <c r="E5" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>116675</v>
+        <v>99802</v>
       </c>
       <c r="D6" t="n">
-        <v>2736</v>
+        <v>2548</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100520</v>
+        <v>72492</v>
       </c>
       <c r="D7" t="n">
-        <v>2556</v>
+        <v>2412</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>99802</v>
+        <v>86001</v>
       </c>
       <c r="D8" t="n">
-        <v>2548</v>
+        <v>2360</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,14 +620,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33852</v>
+        <v>140904</v>
       </c>
       <c r="D9" t="n">
-        <v>1472</v>
+        <v>3436</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -642,14 +642,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45450</v>
+        <v>247089</v>
       </c>
       <c r="D10" t="n">
-        <v>1708</v>
+        <v>6120</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -664,14 +664,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66185</v>
+        <v>120384</v>
       </c>
       <c r="D11" t="n">
-        <v>2088</v>
+        <v>3224</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -686,14 +686,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>247089</v>
+        <v>30464</v>
       </c>
       <c r="D12" t="n">
-        <v>6120</v>
+        <v>1440</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -708,14 +708,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38488</v>
+        <v>341696</v>
       </c>
       <c r="D13" t="n">
-        <v>1676</v>
+        <v>4680</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -730,14 +730,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30464</v>
+        <v>33852</v>
       </c>
       <c r="D14" t="n">
-        <v>1440</v>
+        <v>1472</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>86001</v>
+        <v>45450</v>
       </c>
       <c r="D15" t="n">
-        <v>2360</v>
+        <v>1708</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6528</v>
+        <v>66185</v>
       </c>
       <c r="D16" t="n">
-        <v>736</v>
+        <v>2088</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -800,15 +800,81 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>51295</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>38488</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1676</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6528</v>
+      </c>
+      <c r="D19" t="n">
+        <v>736</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>380</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D20" t="n">
         <v>156</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/roomself_excel/14853.xlsx
+++ b/output/roomself_excel/14853.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>3696</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>3432</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>2736</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +513,6 @@
       <c r="D5" t="n">
         <v>2556</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>2548</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>2412</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>2360</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +577,6 @@
       <c r="D9" t="n">
         <v>3436</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +593,6 @@
       <c r="D10" t="n">
         <v>6120</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +609,6 @@
       <c r="D11" t="n">
         <v>3224</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +625,6 @@
       <c r="D12" t="n">
         <v>1440</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +641,6 @@
       <c r="D13" t="n">
         <v>4680</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +657,6 @@
       <c r="D14" t="n">
         <v>1472</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +673,6 @@
       <c r="D15" t="n">
         <v>1708</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +689,6 @@
       <c r="D16" t="n">
         <v>2088</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +705,6 @@
       <c r="D17" t="n">
         <v>2684</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +721,6 @@
       <c r="D18" t="n">
         <v>1676</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +737,6 @@
       <c r="D19" t="n">
         <v>736</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -870,12 +752,6 @@
       </c>
       <c r="D20" t="n">
         <v>156</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14853.xlsx
+++ b/output/roomself_excel/14853.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
